--- a/Radar_Evolucao_CRM_template.xlsx
+++ b/Radar_Evolucao_CRM_template.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Ra4da45ffe4854e33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leads" sheetId="2" r:id="R24a03c656de54e9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagnosticos" sheetId="3" r:id="Rd25645f4486b4446"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Respostas" sheetId="4" r:id="R3c5b05c7a9ac43b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interacoes" sheetId="5" r:id="R2e4f181533b34d94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracoes" sheetId="6" r:id="Rceb90c706f314604"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicadores" sheetId="7" r:id="R46111da756e44b68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Reda950e2d10d4448"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leads" sheetId="2" r:id="Rc369cf64942144c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diagnosticos" sheetId="3" r:id="Rd442fec9457147ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Respostas" sheetId="4" r:id="R5d6bea9579274f43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interacoes" sheetId="5" r:id="Rc8386ef4520c426d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracoes" sheetId="6" r:id="Rfec91bb28ade4428"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicadores" sheetId="7" r:id="Rb64363642ca54b29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evolucao" sheetId="8" r:id="R2fa677dea9224975"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -517,7 +518,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>RADAR DE EVOLUÇÃO — CRM</x:v>
+        <x:v>RADAR DE EVOLUÇÃO — CRM | PRODUÇÃO</x:v>
       </x:c>
       <x:c r="B1" s="5"/>
       <x:c r="C1" s="5"/>
@@ -611,7 +612,7 @@
       </x:c>
       <x:c r="B4" s="33" t="n">
         <x:f>COUNTA(Leads!A2:A1000)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C4" s="33"/>
       <x:c r="D4" s="33"/>
@@ -644,7 +645,7 @@
       </x:c>
       <x:c r="B5" s="33" t="n">
         <x:f>COUNTA(Diagnosticos!A2:A1000)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C5" s="33"/>
       <x:c r="D5" s="33"/>
@@ -677,7 +678,7 @@
       </x:c>
       <x:c r="B6" s="36" t="n">
         <x:f>IFERROR(AVERAGE(Diagnosticos!D2:D1000),0)</x:f>
-        <x:v>5.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="33"/>
       <x:c r="D6" s="33"/>
@@ -710,7 +711,7 @@
       </x:c>
       <x:c r="B7" s="36" t="n">
         <x:f>IFERROR(LOOKUP(2,1/(Diagnosticos!D2:D1000&lt;&gt;""),Diagnosticos!D2:D1000),0)</x:f>
-        <x:v>5.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C7" s="33"/>
       <x:c r="D7" s="33"/>
@@ -900,18 +901,18 @@
       </x:c>
       <x:c r="B13" s="33" t="n">
         <x:f>COUNT(Diagnosticos!F2:F1000)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C13" s="36" t="n">
         <x:f>IFERROR(AVERAGE(Diagnosticos!F2:F1000),0)</x:f>
-        <x:v>6.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="36" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E13" s="36" t="n">
         <x:f>D13-C13</x:f>
-        <x:v>1.2999999999999998</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F13" s="33" t="str"/>
       <x:c r="G13" s="33" t="str"/>
@@ -941,18 +942,18 @@
       </x:c>
       <x:c r="B14" s="33" t="n">
         <x:f>COUNT(Diagnosticos!G2:G1000)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C14" s="36" t="n">
         <x:f>IFERROR(AVERAGE(Diagnosticos!G2:G1000),0)</x:f>
-        <x:v>5.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="36" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E14" s="36" t="n">
         <x:f>D14-C14</x:f>
-        <x:v>2.9000000000000004</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F14" s="33" t="str"/>
       <x:c r="G14" s="33" t="str"/>
@@ -982,18 +983,18 @@
       </x:c>
       <x:c r="B15" s="33" t="n">
         <x:f>COUNT(Diagnosticos!H2:H1000)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="36" t="n">
         <x:f>IFERROR(AVERAGE(Diagnosticos!H2:H1000),0)</x:f>
-        <x:v>5.4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="36" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E15" s="36" t="n">
         <x:f>D15-C15</x:f>
-        <x:v>2.5999999999999996</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F15" s="33" t="str"/>
       <x:c r="G15" s="33" t="str"/>
@@ -1023,18 +1024,18 @@
       </x:c>
       <x:c r="B16" s="33" t="n">
         <x:f>COUNT(Diagnosticos!I2:I1000)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C16" s="36" t="n">
         <x:f>IFERROR(AVERAGE(Diagnosticos!I2:I1000),0)</x:f>
-        <x:v>7.2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="36" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E16" s="36" t="n">
         <x:f>D16-C16</x:f>
-        <x:v>0.7999999999999998</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F16" s="33" t="str"/>
       <x:c r="G16" s="33" t="str"/>
@@ -1064,18 +1065,18 @@
       </x:c>
       <x:c r="B17" s="33" t="n">
         <x:f>COUNT(Diagnosticos!J2:J1000)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C17" s="36" t="n">
         <x:f>IFERROR(AVERAGE(Diagnosticos!J2:J1000),0)</x:f>
-        <x:v>4.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="36" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E17" s="36" t="n">
         <x:f>D17-C17</x:f>
-        <x:v>3.9000000000000004</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F17" s="33" t="str"/>
       <x:c r="G17" s="33" t="str"/>
@@ -1105,18 +1106,18 @@
       </x:c>
       <x:c r="B18" s="33" t="n">
         <x:f>COUNT(Diagnosticos!K2:K1000)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C18" s="36" t="n">
         <x:f>IFERROR(AVERAGE(Diagnosticos!K2:K1000),0)</x:f>
-        <x:v>4.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="36" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E18" s="36" t="n">
         <x:f>D18-C18</x:f>
-        <x:v>3.2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F18" s="33" t="str"/>
       <x:c r="G18" s="33" t="str"/>
@@ -1146,18 +1147,18 @@
       </x:c>
       <x:c r="B19" s="33" t="n">
         <x:f>COUNT(Diagnosticos!L2:L1000)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C19" s="36" t="n">
         <x:f>IFERROR(AVERAGE(Diagnosticos!L2:L1000),0)</x:f>
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="36" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E19" s="36" t="n">
         <x:f>D19-C19</x:f>
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F19" s="33" t="str"/>
       <x:c r="G19" s="33" t="str"/>
@@ -1187,18 +1188,18 @@
       </x:c>
       <x:c r="B20" s="33" t="n">
         <x:f>COUNT(Diagnosticos!M2:M1000)</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C20" s="36" t="n">
         <x:f>IFERROR(AVERAGE(Diagnosticos!M2:M1000),0)</x:f>
-        <x:v>4.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="36" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E20" s="36" t="n">
         <x:f>D20-C20</x:f>
-        <x:v>3.0999999999999996</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F20" s="33" t="str"/>
       <x:c r="G20" s="33" t="str"/>
@@ -1310,7 +1311,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="38" t="str">
-        <x:v>Use o Dashboard para acompanhar volume, média e evolução. O índice é uma linha de base, não um selo de qualidade. Para comparar ciclos, filtre a aba Diagnosticos por empresa e data.</x:v>
+        <x:v>PRINCÍPIO</x:v>
       </x:c>
       <x:c r="B24" s="33"/>
       <x:c r="C24" s="33"/>
@@ -1339,7 +1340,9 @@
       <x:c r="Z24" s="33"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="33"/>
+      <x:c r="A25" s="33" t="str">
+        <x:v>O índice é uma linha de base, não um selo de qualidade. Para evolução, mantenha um Lead_ID estável e uma linha por diagnóstico na aba Evolucao.</x:v>
+      </x:c>
       <x:c r="B25" s="33"/>
       <x:c r="C25" s="33"/>
       <x:c r="D25" s="33"/>
@@ -6360,40 +6363,18 @@
       <x:c r="Z1" s="33"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="33" t="str">
-        <x:v>LEAD-EXEMPLO</x:v>
-      </x:c>
-      <x:c r="B2" s="46" t="n">
-        <x:v>46273</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="str">
-        <x:v>Exemplo</x:v>
-      </x:c>
-      <x:c r="D2" s="33" t="str">
-        <x:v>Empresa Exemplo</x:v>
-      </x:c>
-      <x:c r="E2" s="33" t="str">
-        <x:v>exemplo@empresa.com</x:v>
-      </x:c>
-      <x:c r="F2" s="33" t="str">
-        <x:v>+55 22 99968-0509</x:v>
-      </x:c>
-      <x:c r="G2" s="33" t="str">
-        <x:v>Gestor</x:v>
-      </x:c>
-      <x:c r="H2" s="33" t="str">
-        <x:v>Landing page</x:v>
-      </x:c>
-      <x:c r="I2" s="33" t="str">
-        <x:v>SIM</x:v>
-      </x:c>
-      <x:c r="J2" s="33" t="str"/>
-      <x:c r="K2" s="33" t="str">
-        <x:v>Retorno diagnóstico</x:v>
-      </x:c>
-      <x:c r="L2" s="33" t="str">
-        <x:v>Novo</x:v>
-      </x:c>
+      <x:c r="A2" s="33"/>
+      <x:c r="B2" s="46"/>
+      <x:c r="C2" s="33"/>
+      <x:c r="D2" s="33"/>
+      <x:c r="E2" s="33"/>
+      <x:c r="F2" s="33"/>
+      <x:c r="G2" s="33"/>
+      <x:c r="H2" s="33"/>
+      <x:c r="I2" s="33"/>
+      <x:c r="J2" s="33"/>
+      <x:c r="K2" s="33"/>
+      <x:c r="L2" s="33"/>
       <x:c r="M2" s="33"/>
       <x:c r="N2" s="33"/>
       <x:c r="O2" s="33"/>
@@ -11964,7 +11945,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdaf5e6b6acde4f2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ad2caac36f44aa7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12058,60 +12039,24 @@
       <x:c r="Z1" s="33"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="33" t="str">
-        <x:v>RE-EXEMPLO</x:v>
-      </x:c>
-      <x:c r="B2" s="46" t="n">
-        <x:v>46273</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="str">
-        <x:v>LEAD-EXEMPLO</x:v>
-      </x:c>
-      <x:c r="D2" s="36" t="n">
-        <x:v>5.8</x:v>
-      </x:c>
-      <x:c r="E2" s="36" t="str">
-        <x:v>Estruturado</x:v>
-      </x:c>
-      <x:c r="F2" s="36" t="n">
-        <x:v>6.7</x:v>
-      </x:c>
-      <x:c r="G2" s="36" t="n">
-        <x:v>5.1</x:v>
-      </x:c>
-      <x:c r="H2" s="36" t="n">
-        <x:v>5.4</x:v>
-      </x:c>
-      <x:c r="I2" s="36" t="n">
-        <x:v>7.2</x:v>
-      </x:c>
-      <x:c r="J2" s="36" t="n">
-        <x:v>4.1</x:v>
-      </x:c>
-      <x:c r="K2" s="36" t="n">
-        <x:v>4.8</x:v>
-      </x:c>
-      <x:c r="L2" s="36" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="M2" s="36" t="n">
-        <x:v>4.9</x:v>
-      </x:c>
-      <x:c r="N2" s="33" t="str">
-        <x:v>Processos</x:v>
-      </x:c>
-      <x:c r="O2" s="33" t="str">
-        <x:v>Tecnologia</x:v>
-      </x:c>
-      <x:c r="P2" s="33" t="str">
-        <x:v>NÃO</x:v>
-      </x:c>
-      <x:c r="Q2" s="33" t="str">
-        <x:v>NÃO</x:v>
-      </x:c>
-      <x:c r="R2" s="33" t="str">
-        <x:v>NÃO</x:v>
-      </x:c>
+      <x:c r="A2" s="33"/>
+      <x:c r="B2" s="46"/>
+      <x:c r="C2" s="33"/>
+      <x:c r="D2" s="36"/>
+      <x:c r="E2" s="36"/>
+      <x:c r="F2" s="36"/>
+      <x:c r="G2" s="36"/>
+      <x:c r="H2" s="36"/>
+      <x:c r="I2" s="36"/>
+      <x:c r="J2" s="36"/>
+      <x:c r="K2" s="36"/>
+      <x:c r="L2" s="36"/>
+      <x:c r="M2" s="36"/>
+      <x:c r="N2" s="33"/>
+      <x:c r="O2" s="33"/>
+      <x:c r="P2" s="33"/>
+      <x:c r="Q2" s="33"/>
+      <x:c r="R2" s="33"/>
       <x:c r="S2" s="33"/>
       <x:c r="T2" s="33"/>
       <x:c r="U2" s="33"/>
@@ -17691,7 +17636,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0cecc0712b1442e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0b7a7dc5bd841bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23328,7 +23273,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8fa64083cdc4e6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3478918dbd5468b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23383,21 +23328,11 @@
       <x:c r="Z1" s="33"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="46" t="n">
-        <x:v>46273</x:v>
-      </x:c>
-      <x:c r="B2" s="33" t="str">
-        <x:v>RE-EXEMPLO</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="str">
-        <x:v>LEAD-EXEMPLO</x:v>
-      </x:c>
-      <x:c r="D2" s="33" t="str">
-        <x:v>diagnostico_concluido</x:v>
-      </x:c>
-      <x:c r="E2" s="33" t="str">
-        <x:v>Avaliação concluída</x:v>
-      </x:c>
+      <x:c r="A2" s="46"/>
+      <x:c r="B2" s="33"/>
+      <x:c r="C2" s="33"/>
+      <x:c r="D2" s="33"/>
+      <x:c r="E2" s="33"/>
       <x:c r="F2" s="33"/>
       <x:c r="G2" s="33"/>
       <x:c r="H2" s="33"/>
@@ -23421,21 +23356,11 @@
       <x:c r="Z2" s="33"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="46" t="n">
-        <x:v>46273</x:v>
-      </x:c>
-      <x:c r="B3" s="33" t="str">
-        <x:v>RE-EXEMPLO</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="str">
-        <x:v>LEAD-EXEMPLO</x:v>
-      </x:c>
-      <x:c r="D3" s="33" t="str">
-        <x:v>lead_registrado</x:v>
-      </x:c>
-      <x:c r="E3" s="33" t="str">
-        <x:v>Cadastro realizado pelo relatório</x:v>
-      </x:c>
+      <x:c r="A3" s="46"/>
+      <x:c r="B3" s="33"/>
+      <x:c r="C3" s="33"/>
+      <x:c r="D3" s="33"/>
+      <x:c r="E3" s="33"/>
       <x:c r="F3" s="33"/>
       <x:c r="G3" s="33"/>
       <x:c r="H3" s="33"/>
@@ -28977,7 +28902,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5e2e0ca7c8c4911"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b51abb7650c41c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -34911,4 +34836,165 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Data</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Lead_ID</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>Diagnostico_ID</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>Empresa</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>Indice_Geral</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>Nivel</x:v>
+      </x:c>
+      <x:c r="G1" t="str">
+        <x:v>Pessoas</x:v>
+      </x:c>
+      <x:c r="H1" t="str">
+        <x:v>Pensamento_Critico</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
+        <x:v>Decisao</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
+        <x:v>Processos</x:v>
+      </x:c>
+      <x:c r="K1" t="str">
+        <x:v>Tecnologia_IA</x:v>
+      </x:c>
+      <x:c r="L1" t="str">
+        <x:v>Dados</x:v>
+      </x:c>
+      <x:c r="M1" t="str">
+        <x:v>Aprendizagem</x:v>
+      </x:c>
+      <x:c r="N1" t="str">
+        <x:v>Inovacao</x:v>
+      </x:c>
+      <x:c r="P1" t="str">
+        <x:v>Resumo</x:v>
+      </x:c>
+      <x:c r="Q1" t="str">
+        <x:v>Valor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="P2" t="str">
+        <x:v>Total de avaliações</x:v>
+      </x:c>
+      <x:c r="Q2" t="n">
+        <x:f>COUNT(A2:A1000)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>COMO USAR</x:v>
+      </x:c>
+      <x:c r="B3" t="str"/>
+      <x:c r="C3" t="str"/>
+      <x:c r="D3" t="str"/>
+      <x:c r="E3" t="str"/>
+      <x:c r="F3" t="str"/>
+      <x:c r="G3" t="str"/>
+      <x:c r="H3" t="str"/>
+      <x:c r="I3" t="str"/>
+      <x:c r="J3" t="str"/>
+      <x:c r="K3" t="str"/>
+      <x:c r="L3" t="str"/>
+      <x:c r="M3" t="str"/>
+      <x:c r="N3" t="str"/>
+      <x:c r="P3" t="str">
+        <x:v>Índice médio</x:v>
+      </x:c>
+      <x:c r="Q3" t="n">
+        <x:f>IFERROR(AVERAGE(E2:E1000),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Esta aba recebe automaticamente um registro por diagnóstico. O mesmo Lead_ID pode aparecer em várias linhas, permitindo acompanhar a evolução ao longo do tempo.</x:v>
+      </x:c>
+      <x:c r="B4" t="str"/>
+      <x:c r="C4" t="str"/>
+      <x:c r="D4" t="str"/>
+      <x:c r="E4" t="str"/>
+      <x:c r="F4" t="str"/>
+      <x:c r="G4" t="str"/>
+      <x:c r="H4" t="str"/>
+      <x:c r="I4" t="str"/>
+      <x:c r="J4" t="str"/>
+      <x:c r="K4" t="str"/>
+      <x:c r="L4" t="str"/>
+      <x:c r="M4" t="str"/>
+      <x:c r="N4" t="str"/>
+      <x:c r="P4" t="str">
+        <x:v>Maior índice</x:v>
+      </x:c>
+      <x:c r="Q4" t="n">
+        <x:f>IFERROR(MAX(E2:E1000),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Leia o histórico por Lead_ID e Data para comparar avaliações. A evolução deve ser observada por índice geral e pelas oito dimensões.</x:v>
+      </x:c>
+      <x:c r="B5" t="str"/>
+      <x:c r="C5" t="str"/>
+      <x:c r="D5" t="str"/>
+      <x:c r="E5" t="str"/>
+      <x:c r="F5" t="str"/>
+      <x:c r="G5" t="str"/>
+      <x:c r="H5" t="str"/>
+      <x:c r="I5" t="str"/>
+      <x:c r="J5" t="str"/>
+      <x:c r="K5" t="str"/>
+      <x:c r="L5" t="str"/>
+      <x:c r="M5" t="str"/>
+      <x:c r="N5"/>
+      <x:c r="P5" t="str">
+        <x:v>Menor índice</x:v>
+      </x:c>
+      <x:c r="Q5" t="n">
+        <x:f>IFERROR(MIN(E2:E1000),0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Fonte dos registros: Google Apps Script do Radar de Evolução.</x:v>
+      </x:c>
+      <x:c r="B6" t="str"/>
+      <x:c r="C6" t="str"/>
+      <x:c r="D6" t="str"/>
+      <x:c r="E6" t="str"/>
+      <x:c r="F6" t="str"/>
+      <x:c r="G6" t="str"/>
+      <x:c r="H6" t="str"/>
+      <x:c r="I6" t="str"/>
+      <x:c r="J6" t="str"/>
+      <x:c r="K6" t="str"/>
+      <x:c r="L6" t="str"/>
+      <x:c r="M6" t="str"/>
+      <x:c r="N6"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>